--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -3137,7 +3137,7 @@
         <v>111120192</v>
       </c>
       <c r="B23" t="n">
-        <v>90207</v>
+        <v>90217</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -3137,7 +3137,7 @@
         <v>111120192</v>
       </c>
       <c r="B23" t="n">
-        <v>90217</v>
+        <v>90229</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -3137,7 +3137,7 @@
         <v>111120192</v>
       </c>
       <c r="B23" t="n">
-        <v>90229</v>
+        <v>90230</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -3137,7 +3137,7 @@
         <v>111120192</v>
       </c>
       <c r="B23" t="n">
-        <v>90230</v>
+        <v>90233</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -3137,7 +3137,7 @@
         <v>111120192</v>
       </c>
       <c r="B23" t="n">
-        <v>90233</v>
+        <v>90239</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790887</v>
+        <v>111119600</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haxängberget, ca 400 m norr om, Jmt</t>
+          <t>Haxängänget, Haxängänget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502034.1759131065</v>
+        <v>502198</v>
       </c>
       <c r="R2" t="n">
-        <v>6984944.599433596</v>
+        <v>6984921</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,58 +757,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790880</v>
+        <v>96790872</v>
       </c>
       <c r="B3" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5734</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502129.2864169817</v>
+        <v>502228</v>
       </c>
       <c r="R3" t="n">
-        <v>6984956.022144424</v>
+        <v>6984974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +841,11 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +858,11 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>gammal kalkbarrskog med både gran och tall</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>döende sälg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790874</v>
+        <v>96790888</v>
       </c>
       <c r="B4" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5747</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502228.5142864292</v>
+        <v>502012</v>
       </c>
       <c r="R4" t="n">
-        <v>6984935.182507762</v>
+        <v>6984962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,21 +948,11 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1009,6 +965,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>gammal kalkbarrskog med både gran och tall</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>äldre sälg, 20 cm bred och lutande</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790882</v>
+        <v>96790887</v>
       </c>
       <c r="B5" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5734</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502106.9720110917</v>
+        <v>502034</v>
       </c>
       <c r="R5" t="n">
-        <v>6984977.82244921</v>
+        <v>6984945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1055,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96790883</v>
+        <v>96790870</v>
       </c>
       <c r="B6" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>1988</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502136.5407270897</v>
+        <v>502284</v>
       </c>
       <c r="R6" t="n">
-        <v>6984997.838489248</v>
+        <v>6984951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1157,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96790881</v>
+        <v>96790877</v>
       </c>
       <c r="B7" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1988</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502143.8313352445</v>
+        <v>502203</v>
       </c>
       <c r="R7" t="n">
-        <v>6984984.20912136</v>
+        <v>6984937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1259,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,37 +1293,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96790888</v>
+        <v>96790875</v>
       </c>
       <c r="B8" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502011.8651531131</v>
+        <v>502219</v>
       </c>
       <c r="R8" t="n">
-        <v>6984961.401235291</v>
+        <v>6984937</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,21 +1361,11 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,11 +1378,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>äldre sälg, 20 cm bred och lutande</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1499,15 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96790873</v>
+        <v>96790881</v>
       </c>
       <c r="B9" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1539,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502223.5204718847</v>
+        <v>502144</v>
       </c>
       <c r="R9" t="n">
-        <v>6984916.999857506</v>
+        <v>6984984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,19 +1463,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96790886</v>
+        <v>96790874</v>
       </c>
       <c r="B10" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1522,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502040.0872168665</v>
+        <v>502228</v>
       </c>
       <c r="R10" t="n">
-        <v>6984952.783729696</v>
+        <v>6984935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,19 +1565,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96790872</v>
+        <v>96790886</v>
       </c>
       <c r="B11" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502228.0324462825</v>
+        <v>502040</v>
       </c>
       <c r="R11" t="n">
-        <v>6984974.267197994</v>
+        <v>6984953</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,21 +1667,11 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1833,11 +1684,6 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>döende sälg</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1855,15 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96790884</v>
+        <v>111187578</v>
       </c>
       <c r="B12" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,37 +1712,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1435</v>
+        <v>5747</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Haxängberget, ca 400 m norr om, Jmt</t>
+          <t>Haxängberget, Haxängberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502087.3809452442</v>
+        <v>502032</v>
       </c>
       <c r="R12" t="n">
-        <v>6985011.44072146</v>
+        <v>6984976</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,22 +1769,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,60 +1783,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96790870</v>
+        <v>96790871</v>
       </c>
       <c r="B13" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1988</v>
+        <v>5754</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2012,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502284.0269994868</v>
+        <v>502274</v>
       </c>
       <c r="R13" t="n">
-        <v>6984950.67322519</v>
+        <v>6984950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,19 +1870,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,15 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96790871</v>
+        <v>96790873</v>
       </c>
       <c r="B14" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502274.0152387377</v>
+        <v>502224</v>
       </c>
       <c r="R14" t="n">
-        <v>6984949.757266573</v>
+        <v>6984917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,19 +1972,9 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,15 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96790875</v>
+        <v>111115983</v>
       </c>
       <c r="B15" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,37 +2017,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Haxängberget, ca 400 m norr om, Jmt</t>
+          <t>Haxängänget, Haxängänget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502219.4108273479</v>
+        <v>502199</v>
       </c>
       <c r="R15" t="n">
-        <v>6984936.994211884</v>
+        <v>6984973</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,22 +2074,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lodyta</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,76 +2093,68 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96790877</v>
+        <v>111115919</v>
       </c>
       <c r="B16" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>220204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Haxängberget, ca 400 m norr om, Jmt</t>
+          <t>Haxängänget, Haxängänget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502203.4819500035</v>
+        <v>502222</v>
       </c>
       <c r="R16" t="n">
-        <v>6984936.983399813</v>
+        <v>6984971</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,22 +2178,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,72 +2194,64 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog med både gran och tall</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111117771</v>
+        <v>111115978</v>
       </c>
       <c r="B17" t="n">
-        <v>99413</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>229504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Haxängberget (Haxängberget), Jmt</t>
+          <t>Haxängänget, Haxängänget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502162.4857801876</v>
+        <v>502205</v>
       </c>
       <c r="R17" t="n">
-        <v>6984991.493007575</v>
+        <v>6984972</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2514,19 +2281,14 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lodyta</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,6 +2297,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2553,37 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111115978</v>
+        <v>111120192</v>
       </c>
       <c r="B18" t="n">
-        <v>78623</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91420</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229504</v>
+        <v>256335</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2592,14 +2350,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Haxängänget (Haxängänget), Jmt</t>
+          <t>Haxängberget, Haxängberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502204.8235997765</v>
+        <v>502141</v>
       </c>
       <c r="R18" t="n">
-        <v>6984971.979036715</v>
+        <v>6984989</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2629,24 +2387,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lodyta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,54 +2417,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111115919</v>
+        <v>96790884</v>
       </c>
       <c r="B19" t="n">
-        <v>106732</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220204</v>
+        <v>1435</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Haxängänget (Haxängänget), Jmt</t>
+          <t>Haxängberget, ca 400 m norr om, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502221.6631376348</v>
+        <v>502088</v>
       </c>
       <c r="R19" t="n">
-        <v>6984971.081527092</v>
+        <v>6985011</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2745,22 +2482,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,69 +2498,67 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog med både gran och tall</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111115983</v>
+        <v>111116011</v>
       </c>
       <c r="B20" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2082</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Haxängänget (Haxängänget), Jmt</t>
+          <t>Haxängänget, Haxängänget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502198.9066096816</v>
+        <v>502203</v>
       </c>
       <c r="R20" t="n">
-        <v>6984972.883986787</v>
+        <v>6984991</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2863,33 +2588,17 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lodyta</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2908,54 +2617,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111116011</v>
+        <v>96790883</v>
       </c>
       <c r="B21" t="n">
-        <v>97565</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2082</v>
+        <v>5754</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Haxängänget (Haxängänget), Jmt</t>
+          <t>Haxängberget, ca 400 m norr om, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502202.5351659534</v>
+        <v>502136</v>
       </c>
       <c r="R21" t="n">
-        <v>6984991.065364953</v>
+        <v>6984998</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2979,22 +2682,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,31 +2698,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog med både gran och tall</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111119600</v>
+        <v>111117771</v>
       </c>
       <c r="B22" t="n">
-        <v>96346</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,35 +2730,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>620</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Haxängänget (Haxängänget), Jmt</t>
+          <t>Haxängberget, Haxängberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502198.48677184</v>
+        <v>502162</v>
       </c>
       <c r="R22" t="n">
-        <v>6984920.618724592</v>
+        <v>6984991</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3095,19 +2788,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,218 +2814,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>111120192</v>
-      </c>
-      <c r="B23" t="n">
-        <v>90239</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>256335</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Ramaria karstenii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Haxängberget, Haxängberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>502141</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6984989</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>111187578</v>
-      </c>
-      <c r="B24" t="n">
-        <v>88956</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5747</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Läderdoftande fingersvamp</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Haxängberget (Haxängberget), Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>502032</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6984976</v>
-      </c>
-      <c r="S24" t="n">
-        <v>40</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30683-2023 artfynd.xlsx
+++ b/artfynd/A 30683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111119600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790887</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790870</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790877</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111116011</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790875</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790881</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790874</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790886</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111187578</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790871</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790873</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790883</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111115983</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2509,6 +2599,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111115919</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2607,6 +2702,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111117771</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111115978</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,8 +2919,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111120192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>